--- a/grupos/3AEV - Estadisticos 20211.xlsx
+++ b/grupos/3AEV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="154">
   <si>
     <t>Materia</t>
   </si>
@@ -185,21 +185,21 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
+    <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,46 +221,160 @@
     <t>CANUTO</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>XILCAHUA</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>AMANDA MICHEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>AVENDAÑO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CHAVEZ</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>GUILLEN</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
+    <t>MAYAHUA</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>SILVESTRE</t>
@@ -269,28 +383,13 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
+    <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>MENDEZ</t>
@@ -302,31 +401,25 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
+    <t>TEMOXTLE</t>
   </si>
   <si>
     <t>BAROJAS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>CASTRO</t>
   </si>
   <si>
     <t>ALAMILLO</t>
   </si>
   <si>
-    <t>XILCAHUA</t>
-  </si>
-  <si>
-    <t>JOAQUIN</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>URBINA</t>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
   </si>
   <si>
     <t>ARIAS</t>
@@ -335,28 +428,19 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>AXEL JESUS</t>
+  </si>
+  <si>
+    <t>KARLA JOVANA</t>
   </si>
   <si>
     <t>NORKYS AIRY</t>
   </si>
   <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
+    <t>JORGE HUMBERTO</t>
   </si>
   <si>
     <t>CRISTIAN JAHIR</t>
@@ -368,115 +452,31 @@
     <t>ANGEL</t>
   </si>
   <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
+    <t>ELIAS</t>
   </si>
   <si>
     <t>DIEGO IVAN</t>
   </si>
   <si>
-    <t>DAVID</t>
-  </si>
-  <si>
     <t>JOHAN ALEJANDRO</t>
   </si>
   <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>AMANDA MICHEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
   </si>
   <si>
     <t>YAIR</t>
   </si>
   <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
     <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>AVENDAÑO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>AXEL JESUS</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
-  </si>
-  <si>
-    <t>JORGE HUMBERTO</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
   </si>
   <si>
     <t>AYLIN MELISSA</t>
@@ -983,22 +983,22 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1019,7 +1019,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -1031,7 +1031,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -1042,7 +1042,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -1054,7 +1054,7 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1072,10 +1072,10 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1096,7 +1096,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -1108,7 +1108,7 @@
         <v>-1</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1119,7 +1119,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -1152,7 +1152,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1173,7 +1173,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -1188,7 +1188,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1196,7 +1196,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1229,7 +1229,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1250,7 +1250,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -1265,7 +1265,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1291,22 +1291,22 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1327,7 +1327,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1342,7 +1342,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1362,7 +1362,7 @@
         <v>8</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1374,7 +1374,7 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1383,7 +1383,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1416,7 +1416,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1445,22 +1445,22 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1504,7 +1504,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -1516,7 +1516,7 @@
         <v>-1</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -1537,7 +1537,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1558,7 +1558,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>5</v>
@@ -1570,7 +1570,7 @@
         <v>-1</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1581,7 +1581,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -1614,7 +1614,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1635,7 +1635,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>5</v>
@@ -1658,7 +1658,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -1670,7 +1670,7 @@
         <v>-1</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1691,7 +1691,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1712,7 +1712,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1724,7 +1724,7 @@
         <v>-1</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1735,7 +1735,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -1747,7 +1747,7 @@
         <v>7</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G14">
         <v>6</v>
@@ -1768,7 +1768,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1801,10 +1801,10 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1812,7 +1812,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1845,7 +1845,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1866,7 +1866,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -1881,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1889,7 +1889,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1901,7 +1901,7 @@
         <v>7</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -1943,7 +1943,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -1955,7 +1955,7 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1978,7 +1978,7 @@
         <v>-1</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -1996,10 +1996,10 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2032,7 +2032,7 @@
         <v>-1</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -2061,22 +2061,22 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2097,13 +2097,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>8</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2112,7 +2112,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2120,7 +2120,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -2132,7 +2132,7 @@
         <v>-1</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2153,7 +2153,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2174,7 +2174,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -2186,7 +2186,7 @@
         <v>-1</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2197,7 +2197,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -2215,13 +2215,13 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2230,7 +2230,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2251,13 +2251,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>8</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2298,16 +2298,16 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2334,16 +2334,16 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>8</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2384,7 +2384,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2428,7 +2428,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -2446,7 +2446,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2458,10 +2458,10 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2482,7 +2482,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>5</v>
@@ -2505,7 +2505,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>5</v>
@@ -2517,7 +2517,7 @@
         <v>-1</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -2538,7 +2538,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2559,7 +2559,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2571,7 +2571,7 @@
         <v>-1</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2600,22 +2600,22 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2642,13 +2642,13 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>8</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2659,7 +2659,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -2671,7 +2671,7 @@
         <v>-1</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -2692,7 +2692,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2713,7 +2713,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>5</v>
@@ -2725,7 +2725,7 @@
         <v>-1</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2769,7 +2769,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2805,7 +2805,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2831,22 +2831,22 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2867,7 +2867,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>9</v>
@@ -2879,10 +2879,10 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2923,7 +2923,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2967,7 +2967,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>6</v>
@@ -2979,7 +2979,7 @@
         <v>-1</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -2991,7 +2991,7 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3000,7 +3000,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3021,7 +3021,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>6</v>
@@ -3033,7 +3033,7 @@
         <v>-1</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -3044,19 +3044,19 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>5</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>-1</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -3077,7 +3077,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3098,19 +3098,19 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>-1</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3133,28 +3133,28 @@
         <v>6</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G32">
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3181,16 +3181,16 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>6</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3231,7 +3231,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3275,7 +3275,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>6</v>
@@ -3287,13 +3287,13 @@
         <v>7</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G34">
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3308,7 +3308,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3329,7 +3329,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>6</v>
@@ -3341,10 +3341,10 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3385,7 +3385,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3447,22 +3447,22 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3483,13 +3483,13 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>5</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>-1</v>
@@ -3563,19 +3563,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>42.42</v>
+        <v>33.33</v>
       </c>
       <c r="G2">
-        <v>57.58</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3595,30 +3595,30 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>48.48</v>
+        <v>57.58</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J3">
-        <v>51.52</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3627,30 +3627,30 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>63.64</v>
+      </c>
+      <c r="G4">
+        <v>36.36</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>57.58</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>7.4</v>
-      </c>
-      <c r="I4">
-        <v>14</v>
-      </c>
-      <c r="J4">
-        <v>42.42</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3659,30 +3659,30 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>63.64</v>
+      </c>
+      <c r="G5">
+        <v>36.36</v>
+      </c>
+      <c r="H5">
+        <v>6.5</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>57.58</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>42.42</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3691,30 +3691,30 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="G6">
-        <v>36.36</v>
+        <v>21.21</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -3723,25 +3723,25 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>63.64</v>
+        <v>72.73</v>
       </c>
       <c r="G7">
-        <v>21.21</v>
+        <v>27.27</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>15.15</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3751,7 +3751,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3786,13 +3786,13 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>55</v>
@@ -3800,119 +3800,119 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920071</v>
+        <v>20330051920072</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920071</v>
+        <v>20330051920073</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920072</v>
+        <v>19330051920051</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920072</v>
+        <v>19330051920051</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920073</v>
+        <v>20330051920077</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920073</v>
+        <v>20330051920077</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
@@ -3920,59 +3920,59 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920074</v>
+        <v>20330051920080</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920051</v>
+        <v>20330051920087</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920051</v>
+        <v>20330051920089</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>55</v>
@@ -3980,79 +3980,79 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920051</v>
+        <v>20330051920092</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920051</v>
+        <v>18330051920074</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
         <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920077</v>
+        <v>18330051920074</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920077</v>
+        <v>20330051920059</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
         <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
         <v>55</v>
@@ -4060,39 +4060,39 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920077</v>
+        <v>20330051920062</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920080</v>
+        <v>20330051920063</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
         <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
         <v>55</v>
@@ -4100,682 +4100,42 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920080</v>
+        <v>20330051920065</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920080</v>
+        <v>20330051920386</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920081</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920081</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920082</v>
-      </c>
-      <c r="B22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920084</v>
-      </c>
-      <c r="B23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920084</v>
-      </c>
-      <c r="B24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" t="s">
-        <v>93</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920087</v>
-      </c>
-      <c r="B25" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920087</v>
-      </c>
-      <c r="B26" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920089</v>
-      </c>
-      <c r="B27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>117</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920089</v>
-      </c>
-      <c r="B28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" t="s">
-        <v>117</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920089</v>
-      </c>
-      <c r="B29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" t="s">
-        <v>117</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920090</v>
-      </c>
-      <c r="B30" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920092</v>
-      </c>
-      <c r="B31" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" t="s">
-        <v>119</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920093</v>
-      </c>
-      <c r="B32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" t="s">
-        <v>120</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>18330051920074</v>
-      </c>
-      <c r="B33" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" t="s">
-        <v>121</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>18330051920074</v>
-      </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" t="s">
-        <v>121</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>18330051920074</v>
-      </c>
-      <c r="B35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" t="s">
-        <v>121</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>18330051920074</v>
-      </c>
-      <c r="B36" t="s">
-        <v>76</v>
-      </c>
-      <c r="C36" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" t="s">
-        <v>121</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920059</v>
-      </c>
-      <c r="B37" t="s">
-        <v>77</v>
-      </c>
-      <c r="C37" t="s">
-        <v>100</v>
-      </c>
-      <c r="D37" t="s">
-        <v>122</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920059</v>
-      </c>
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" t="s">
-        <v>122</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920059</v>
-      </c>
-      <c r="B39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>100</v>
-      </c>
-      <c r="D39" t="s">
-        <v>122</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920062</v>
-      </c>
-      <c r="B40" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" t="s">
-        <v>77</v>
-      </c>
-      <c r="D40" t="s">
-        <v>123</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920063</v>
-      </c>
-      <c r="B41" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" t="s">
-        <v>101</v>
-      </c>
-      <c r="D41" t="s">
-        <v>124</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920063</v>
-      </c>
-      <c r="B42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" t="s">
-        <v>124</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920063</v>
-      </c>
-      <c r="B43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" t="s">
-        <v>101</v>
-      </c>
-      <c r="D43" t="s">
-        <v>124</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920065</v>
-      </c>
-      <c r="B44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" t="s">
-        <v>102</v>
-      </c>
-      <c r="D44" t="s">
-        <v>125</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920065</v>
-      </c>
-      <c r="B45" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" t="s">
-        <v>102</v>
-      </c>
-      <c r="D45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E45" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920065</v>
-      </c>
-      <c r="B46" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920065</v>
-      </c>
-      <c r="B47" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" t="s">
-        <v>102</v>
-      </c>
-      <c r="D47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920066</v>
-      </c>
-      <c r="B48" t="s">
-        <v>81</v>
-      </c>
-      <c r="C48" t="s">
-        <v>103</v>
-      </c>
-      <c r="D48" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920070</v>
-      </c>
-      <c r="B49" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" t="s">
-        <v>104</v>
-      </c>
-      <c r="D49" t="s">
-        <v>127</v>
-      </c>
-      <c r="E49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920070</v>
-      </c>
-      <c r="B50" t="s">
-        <v>82</v>
-      </c>
-      <c r="C50" t="s">
-        <v>104</v>
-      </c>
-      <c r="D50" t="s">
-        <v>127</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920386</v>
-      </c>
-      <c r="B51" t="s">
-        <v>83</v>
-      </c>
-      <c r="C51" t="s">
-        <v>105</v>
-      </c>
-      <c r="D51" t="s">
-        <v>128</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4814,50 +4174,50 @@
         <v>19330051920051</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>18330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920065</v>
+        <v>18330051920074</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
         <v>102</v>
       </c>
-      <c r="D4" t="s">
-        <v>125</v>
-      </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4868,347 +4228,347 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920077</v>
+        <v>20330051920072</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920080</v>
+        <v>20330051920073</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920089</v>
+        <v>20330051920080</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920059</v>
+        <v>20330051920087</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920063</v>
+        <v>20330051920089</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920072</v>
+        <v>20330051920092</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920073</v>
+        <v>20330051920059</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920081</v>
+        <v>20330051920062</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920084</v>
+        <v>20330051920063</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920087</v>
+        <v>20330051920065</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920070</v>
+        <v>20330051920386</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920074</v>
+        <v>20330051920041</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="C17" t="s">
         <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920082</v>
+        <v>20330051920359</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920090</v>
+        <v>20330051920074</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920092</v>
+        <v>20330051920075</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920093</v>
+        <v>20330051920081</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920062</v>
+        <v>20330051920082</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920066</v>
+        <v>20330051920084</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920386</v>
+        <v>20330051920088</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920041</v>
+        <v>20330051920090</v>
       </c>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -5219,16 +4579,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920359</v>
+        <v>20330051920091</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5236,16 +4596,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920075</v>
+        <v>20330051920093</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5253,16 +4613,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920088</v>
+        <v>20330051920058</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5270,16 +4630,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920091</v>
+        <v>20330051920061</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5287,13 +4647,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920058</v>
+        <v>20330051920064</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D30" t="s">
         <v>149</v>
@@ -5304,13 +4664,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920061</v>
+        <v>20330051920066</v>
       </c>
       <c r="B31" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s">
         <v>150</v>
@@ -5321,13 +4681,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920064</v>
+        <v>20330051920068</v>
       </c>
       <c r="B32" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
         <v>151</v>
@@ -5338,13 +4698,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920068</v>
+        <v>20330051920070</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
         <v>152</v>
@@ -5358,10 +4718,10 @@
         <v>20330051920069</v>
       </c>
       <c r="B34" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D34" t="s">
         <v>153</v>
@@ -5377,7 +4737,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5409,111 +4769,111 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920072</v>
+        <v>20330051920093</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920072</v>
+        <v>20330051920093</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920073</v>
+        <v>20330051920070</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920073</v>
+        <v>20330051920070</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920081</v>
+        <v>20330051920072</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>55</v>
@@ -5527,22 +4887,22 @@
         <v>20330051920081</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5550,36 +4910,36 @@
         <v>20330051920082</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920082</v>
+        <v>20330051920061</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5593,116 +4953,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920070</v>
+        <v>20330051920069</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920070</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920090</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920066</v>
-      </c>
-      <c r="B13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920069</v>
-      </c>
-      <c r="B14" t="s">
-        <v>137</v>
-      </c>
-      <c r="C14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEV - Estadisticos 20211.xlsx
+++ b/grupos/3AEV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="154">
   <si>
     <t>Materia</t>
   </si>
@@ -185,12 +185,12 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -212,274 +212,274 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>XILCAHUA</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>AVENDAÑO</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
     <t>MIXCOHA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>ROSETE</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>ZGAIP</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>LEON</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
     <t>EVARISTO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XILCAHUA</t>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>BELLO</t>
   </si>
   <si>
     <t>JOAQUIN</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>SALAS</t>
   </si>
   <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
     <t>URBINA</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>OJEDA</t>
   </si>
   <si>
+    <t>AXEL JESUS</t>
+  </si>
+  <si>
     <t>MARCO ANTONIO</t>
   </si>
   <si>
     <t>PAUL ARAVIER</t>
   </si>
   <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
+    <t>KARLA JOVANA</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
+  </si>
+  <si>
+    <t>JORGE HUMBERTO</t>
   </si>
   <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
     <t>GABRIEL JOSUE</t>
   </si>
   <si>
+    <t>ELIAS</t>
+  </si>
+  <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
+    <t>DIEGO IVAN</t>
+  </si>
+  <si>
     <t>DAVID</t>
   </si>
   <si>
-    <t>JUAN CARLOS</t>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
   </si>
   <si>
     <t>DANIEL</t>
   </si>
   <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
     <t>AMANDA MICHEL</t>
   </si>
   <si>
     <t>VICTOR GAEL</t>
   </si>
   <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
     <t>ALDIR ADALBERTO</t>
   </si>
   <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
     <t>YAEL</t>
-  </si>
-  <si>
-    <t>AVENDAÑO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>AXEL JESUS</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
-  </si>
-  <si>
-    <t>NORKYS AIRY</t>
-  </si>
-  <si>
-    <t>JORGE HUMBERTO</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>DIEGO IVAN</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
   </si>
 </sst>
 </file>
@@ -986,13 +986,13 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -1022,13 +1022,13 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1051,7 +1051,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -1063,7 +1063,7 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1105,7 +1105,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1140,13 +1140,13 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1176,13 +1176,13 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1205,7 +1205,7 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>8</v>
@@ -1217,7 +1217,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1253,13 +1253,13 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>8</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1294,13 +1294,13 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1371,13 +1371,13 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1413,7 +1413,7 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1448,13 +1448,13 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>8</v>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1513,7 +1513,7 @@
         <v>-1</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -1525,7 +1525,7 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1567,7 +1567,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1590,7 +1590,7 @@
         <v>-1</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>8</v>
@@ -1602,7 +1602,7 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1644,7 +1644,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1667,7 +1667,7 @@
         <v>7</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1679,7 +1679,7 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1721,7 +1721,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1756,13 +1756,13 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1792,7 +1792,7 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1833,13 +1833,13 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1869,13 +1869,13 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1910,13 +1910,13 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1952,7 +1952,7 @@
         <v>5</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -1975,7 +1975,7 @@
         <v>5</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>8</v>
@@ -1987,13 +1987,13 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>7</v>
@@ -2029,7 +2029,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2064,13 +2064,13 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -2100,7 +2100,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -2129,7 +2129,7 @@
         <v>8</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -2141,7 +2141,7 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2183,7 +2183,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2218,13 +2218,13 @@
         <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2295,13 +2295,13 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -2331,13 +2331,13 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2360,7 +2360,7 @@
         <v>5</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>7</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2414,7 +2414,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2449,13 +2449,13 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2491,7 +2491,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2514,7 +2514,7 @@
         <v>-1</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -2526,7 +2526,7 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2568,7 +2568,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2603,13 +2603,13 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2668,7 +2668,7 @@
         <v>6</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -2680,7 +2680,7 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2722,7 +2722,7 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2757,13 +2757,13 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2793,7 +2793,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -2834,13 +2834,13 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -2899,7 +2899,7 @@
         <v>5</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F29">
         <v>9</v>
@@ -2911,7 +2911,7 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -2947,13 +2947,13 @@
         <v>6</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>5</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -2976,7 +2976,7 @@
         <v>5</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F30">
         <v>10</v>
@@ -2988,7 +2988,7 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>6</v>
@@ -3024,13 +3024,13 @@
         <v>5</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V30">
         <v>5</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -3053,7 +3053,7 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F31">
         <v>5</v>
@@ -3065,13 +3065,13 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3107,7 +3107,7 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X31">
         <v>5</v>
@@ -3142,13 +3142,13 @@
         <v>6</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -3178,13 +3178,13 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>7</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3219,13 +3219,13 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3261,7 +3261,7 @@
         <v>5</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3296,13 +3296,13 @@
         <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3332,7 +3332,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -3373,13 +3373,13 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3415,7 +3415,7 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3438,7 +3438,7 @@
         <v>6</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F36">
         <v>10</v>
@@ -3450,13 +3450,13 @@
         <v>9</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
         <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -3486,13 +3486,13 @@
         <v>9</v>
       </c>
       <c r="U36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>7</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3598,27 +3598,27 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>57.58</v>
       </c>
       <c r="G3">
+        <v>42.42</v>
+      </c>
+      <c r="H3">
+        <v>6.5</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="H3">
-        <v>7.4</v>
-      </c>
-      <c r="I3">
-        <v>14</v>
-      </c>
       <c r="J3">
-        <v>42.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3627,19 +3627,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>63.64</v>
+        <v>57.58</v>
       </c>
       <c r="G4">
-        <v>36.36</v>
+        <v>42.42</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3751,7 +3751,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3780,56 +3780,56 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920071</v>
+        <v>20330051920073</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920072</v>
+        <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920073</v>
+        <v>20330051920077</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -3840,302 +3840,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920051</v>
+        <v>18330051920074</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920051</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920077</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920077</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920080</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920087</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920089</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920092</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>18330051920074</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>18330051920074</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920059</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920062</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920063</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920065</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920386</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4171,67 +3891,67 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920051</v>
+        <v>20330051920073</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920077</v>
+        <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>18330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920071</v>
+        <v>18330051920074</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -4239,200 +3959,200 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920072</v>
+        <v>20330051920041</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920073</v>
+        <v>20330051920071</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920080</v>
+        <v>20330051920072</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920087</v>
+        <v>20330051920359</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920089</v>
+        <v>20330051920074</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920092</v>
+        <v>20330051920075</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920059</v>
+        <v>20330051920080</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920062</v>
+        <v>20330051920081</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920063</v>
+        <v>20330051920082</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920065</v>
+        <v>20330051920084</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920386</v>
+        <v>20330051920087</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920041</v>
+        <v>20330051920088</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
         <v>137</v>
@@ -4443,13 +4163,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920359</v>
+        <v>20330051920089</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
         <v>138</v>
@@ -4460,13 +4180,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920074</v>
+        <v>20330051920090</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
         <v>139</v>
@@ -4477,16 +4197,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920075</v>
+        <v>20330051920091</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4494,16 +4214,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920081</v>
+        <v>20330051920092</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4511,16 +4231,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920082</v>
+        <v>20330051920093</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4528,16 +4248,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920084</v>
+        <v>20330051920058</v>
       </c>
       <c r="B23" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4545,16 +4265,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920088</v>
+        <v>20330051920059</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4562,16 +4282,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920090</v>
+        <v>20330051920061</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4579,16 +4299,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920091</v>
+        <v>20330051920062</v>
       </c>
       <c r="B26" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4596,13 +4316,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920093</v>
+        <v>20330051920063</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s">
         <v>146</v>
@@ -4613,13 +4333,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920058</v>
+        <v>20330051920064</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
         <v>147</v>
@@ -4630,13 +4350,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920061</v>
+        <v>20330051920065</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
         <v>148</v>
@@ -4647,13 +4367,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920064</v>
+        <v>20330051920066</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
         <v>149</v>
@@ -4664,13 +4384,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920066</v>
+        <v>20330051920068</v>
       </c>
       <c r="B31" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
         <v>150</v>
@@ -4681,13 +4401,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920068</v>
+        <v>20330051920070</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
         <v>151</v>
@@ -4698,13 +4418,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920070</v>
+        <v>20330051920069</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s">
         <v>152</v>
@@ -4715,13 +4435,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920069</v>
+        <v>20330051920386</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
         <v>153</v>
@@ -4769,22 +4489,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920093</v>
+        <v>20330051920072</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4792,22 +4512,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920093</v>
+        <v>20330051920072</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4815,22 +4535,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920070</v>
+        <v>20330051920087</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4838,16 +4558,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920070</v>
+        <v>20330051920087</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4861,45 +4581,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920072</v>
+        <v>20330051920081</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920081</v>
+        <v>20330051920082</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4907,22 +4627,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920082</v>
+        <v>20330051920061</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4930,16 +4650,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920061</v>
+        <v>20330051920069</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4953,13 +4673,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920069</v>
+        <v>20330051920386</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s">
         <v>153</v>

--- a/grupos/3AEV - Estadisticos 20211.xlsx
+++ b/grupos/3AEV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="154">
   <si>
     <t>Materia</t>
   </si>
@@ -191,13 +191,13 @@
     <t>Silva Villegas Mario</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
     <t>NC</t>
@@ -1060,7 +1060,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>6</v>
@@ -1096,7 +1096,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -1599,7 +1599,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -1753,7 +1753,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1830,7 +1830,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>7</v>
@@ -1866,7 +1866,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -2138,7 +2138,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -2754,7 +2754,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>5</v>
@@ -2985,7 +2985,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>5</v>
@@ -3021,7 +3021,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -3062,7 +3062,7 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -3098,7 +3098,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <v>5</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3659,30 +3659,30 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="G5">
-        <v>36.36</v>
+        <v>21.21</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3691,30 +3691,30 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>66.67</v>
+        <v>72.73</v>
       </c>
       <c r="G6">
-        <v>21.21</v>
+        <v>27.27</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -3723,19 +3723,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>72.73</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="G7">
-        <v>27.27</v>
+        <v>24.24</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3815,7 +3815,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3835,7 +3835,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3855,7 +3855,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4457,7 +4457,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4550,7 +4550,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4604,22 +4604,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920082</v>
+        <v>20330051920061</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4627,16 +4627,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920061</v>
+        <v>20330051920069</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -4650,16 +4650,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920069</v>
+        <v>20330051920386</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4668,29 +4668,6 @@
         <v>54</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920386</v>
-      </c>
-      <c r="B10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEV - Estadisticos 20211.xlsx
+++ b/grupos/3AEV - Estadisticos 20211.xlsx
@@ -3370,7 +3370,7 @@
         <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
         <v>9</v>
@@ -3406,7 +3406,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>9</v>

--- a/grupos/3AEV - Estadisticos 20211.xlsx
+++ b/grupos/3AEV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="154">
   <si>
     <t>Materia</t>
   </si>
@@ -182,24 +182,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,238 +212,238 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AVENDAÑO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>CANUTO</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>ESPINOZA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
     <t>MEDINA</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
     <t>XILCAHUA</t>
   </si>
   <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>AXEL JESUS</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
     <t>ISRAEL</t>
   </si>
   <si>
+    <t>KARLA JOVANA</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
+  </si>
+  <si>
+    <t>JORGE HUMBERTO</t>
+  </si>
+  <si>
     <t>JESUS ISRAEL</t>
   </si>
   <si>
     <t>ADRIAN</t>
   </si>
   <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ELIAS</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DIEGO IVAN</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
     <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>AVENDAÑO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>JOAQUIN</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>AXEL JESUS</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
-  </si>
-  <si>
-    <t>NORKYS AIRY</t>
-  </si>
-  <si>
-    <t>JORGE HUMBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DIEGO IVAN</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
   </si>
   <si>
     <t>ZURIEL ARTURO</t>
@@ -1001,22 +1001,22 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -1031,10 +1031,10 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1066,10 +1066,10 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>7</v>
@@ -1078,37 +1078,37 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>6</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1125,7 +1125,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1137,55 +1137,55 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>5</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>5</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1214,58 +1214,58 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>5</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>5</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1309,22 +1309,22 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1342,7 +1342,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1368,7 +1368,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1380,46 +1380,46 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1463,34 +1463,34 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>8</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1510,7 +1510,7 @@
         <v>5</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -1522,58 +1522,58 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>5</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>5</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1587,7 +1587,7 @@
         <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>5</v>
@@ -1605,34 +1605,34 @@
         <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -1641,13 +1641,13 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>5</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1676,40 +1676,40 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>5</v>
@@ -1718,7 +1718,7 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1759,37 +1759,37 @@
         <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1798,13 +1798,13 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1836,37 +1836,37 @@
         <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1875,13 +1875,13 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1907,40 +1907,40 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -1949,10 +1949,10 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -1984,13 +1984,13 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>6</v>
@@ -2002,40 +2002,40 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2079,22 +2079,22 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2106,7 +2106,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2144,43 +2144,43 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>5</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2227,28 +2227,28 @@
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2260,10 +2260,10 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2292,7 +2292,7 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>7</v>
@@ -2310,28 +2310,28 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2340,7 +2340,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2369,55 +2369,55 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>6</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>5</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2452,7 +2452,7 @@
         <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -2464,40 +2464,40 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2511,7 +2511,7 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -2523,40 +2523,40 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2565,7 +2565,7 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2618,22 +2618,22 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2648,7 +2648,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2677,52 +2677,52 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>5</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2760,34 +2760,34 @@
         <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2796,16 +2796,16 @@
         <v>6</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2849,37 +2849,37 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2908,58 +2908,58 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I29">
         <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2994,49 +2994,49 @@
         <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>6</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3068,49 +3068,49 @@
         <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
         <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>6</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3157,34 +3157,34 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>6</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>7</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3216,55 +3216,55 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
         <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3299,49 +3299,49 @@
         <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
         <v>7</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>6</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3376,52 +3376,52 @@
         <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
         <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>7</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3465,40 +3465,40 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3554,7 +3554,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3563,19 +3563,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>33.33</v>
+        <v>51.52</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>48.48</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3595,19 +3595,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>57.58</v>
+        <v>63.64</v>
       </c>
       <c r="G3">
-        <v>42.42</v>
+        <v>36.36</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3627,19 +3627,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>57.58</v>
+        <v>69.7</v>
       </c>
       <c r="G4">
-        <v>42.42</v>
+        <v>30.3</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3659,30 +3659,30 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>66.67</v>
+        <v>72.73</v>
       </c>
       <c r="G5">
-        <v>21.21</v>
+        <v>27.27</v>
       </c>
       <c r="H5">
         <v>6.9</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3691,19 +3691,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>72.73</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G6">
-        <v>27.27</v>
+        <v>18.18</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -3723,19 +3723,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>75.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>24.24</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3751,7 +3751,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3776,86 +3776,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920073</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920051</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920077</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>18330051920074</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3891,81 +3811,81 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920073</v>
+        <v>20330051920041</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920051</v>
+        <v>20330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920077</v>
+        <v>20330051920072</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>18330051920074</v>
+        <v>20330051920073</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920041</v>
+        <v>20330051920359</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
         <v>126</v>
@@ -3976,13 +3896,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920071</v>
+        <v>20330051920074</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>127</v>
@@ -3993,13 +3913,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920072</v>
+        <v>20330051920075</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
         <v>128</v>
@@ -4010,13 +3930,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920359</v>
+        <v>19330051920051</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
         <v>129</v>
@@ -4027,13 +3947,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
         <v>130</v>
@@ -4044,13 +3964,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920075</v>
+        <v>20330051920080</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
         <v>131</v>
@@ -4061,13 +3981,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920080</v>
+        <v>20330051920081</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
         <v>132</v>
@@ -4078,13 +3998,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920081</v>
+        <v>20330051920082</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
         <v>133</v>
@@ -4095,13 +4015,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920082</v>
+        <v>20330051920084</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
         <v>134</v>
@@ -4112,13 +4032,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920084</v>
+        <v>20330051920087</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
         <v>135</v>
@@ -4129,13 +4049,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920087</v>
+        <v>20330051920088</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>136</v>
@@ -4146,13 +4066,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920088</v>
+        <v>20330051920089</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
         <v>137</v>
@@ -4163,13 +4083,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920089</v>
+        <v>20330051920090</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
         <v>138</v>
@@ -4180,16 +4100,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920090</v>
+        <v>20330051920091</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4197,16 +4117,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920091</v>
+        <v>20330051920092</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4214,13 +4134,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920092</v>
+        <v>20330051920093</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
         <v>140</v>
@@ -4231,13 +4151,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920093</v>
+        <v>18330051920074</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
         <v>141</v>
@@ -4251,10 +4171,10 @@
         <v>20330051920058</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
         <v>142</v>
@@ -4268,10 +4188,10 @@
         <v>20330051920059</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
         <v>143</v>
@@ -4285,10 +4205,10 @@
         <v>20330051920061</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
         <v>144</v>
@@ -4302,10 +4222,10 @@
         <v>20330051920062</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
         <v>145</v>
@@ -4319,10 +4239,10 @@
         <v>20330051920063</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
         <v>146</v>
@@ -4336,10 +4256,10 @@
         <v>20330051920064</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
         <v>147</v>
@@ -4353,10 +4273,10 @@
         <v>20330051920065</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
         <v>148</v>
@@ -4370,10 +4290,10 @@
         <v>20330051920066</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
         <v>149</v>
@@ -4387,10 +4307,10 @@
         <v>20330051920068</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
         <v>150</v>
@@ -4404,10 +4324,10 @@
         <v>20330051920070</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
         <v>151</v>
@@ -4421,10 +4341,10 @@
         <v>20330051920069</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
         <v>152</v>
@@ -4438,10 +4358,10 @@
         <v>20330051920386</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
         <v>153</v>
@@ -4457,7 +4377,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4489,22 +4409,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920072</v>
+        <v>20330051920074</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4512,22 +4432,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920072</v>
+        <v>20330051920074</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4535,22 +4455,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920087</v>
+        <v>19330051920051</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4558,22 +4478,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920087</v>
+        <v>19330051920051</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4581,19 +4501,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920081</v>
+        <v>20330051920065</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
@@ -4604,22 +4524,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920061</v>
+        <v>20330051920065</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4627,19 +4547,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920069</v>
+        <v>20330051920082</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>54</v>
@@ -4650,24 +4570,47 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920386</v>
+        <v>20330051920062</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>54</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920070</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>
